--- a/_annex_A.xlsx
+++ b/_annex_A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\mp\projects\PR0118 - ISO 11171 Calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39F8D72-91E2-4D8F-B3A2-FCDAE587E51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8FEE85-83F5-4E7F-90B4-360445E8ECA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17745" xr2:uid="{953665B5-C50E-440F-B37B-B0E68037AD87}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
   <si>
     <t>Annex A Preliminary Check</t>
   </si>
@@ -180,30 +180,18 @@
     <t>Portion 2</t>
   </si>
   <si>
-    <t>Measure Fluid Density</t>
-  </si>
-  <si>
     <t>Portion 3</t>
   </si>
   <si>
-    <t>Temperature</t>
-  </si>
-  <si>
     <t>Portion 4</t>
   </si>
   <si>
-    <t>100ml Weight</t>
-  </si>
-  <si>
     <t>AVERAGE 10um count/ml</t>
   </si>
   <si>
     <t>Portion 5</t>
   </si>
   <si>
-    <t>Density g/cc</t>
-  </si>
-  <si>
     <t>Expected 10um count/ml</t>
   </si>
   <si>
@@ -211,9 +199,6 @@
   </si>
   <si>
     <t>Mean</t>
-  </si>
-  <si>
-    <t>Full bottle weight</t>
   </si>
   <si>
     <t>Sample StdDev</t>
@@ -265,13 +250,13 @@
     <t>Error</t>
   </si>
   <si>
-    <t>11171-00066</t>
-  </si>
-  <si>
-    <t>LPA4</t>
-  </si>
-  <si>
-    <t>11171-00065</t>
+    <t>REF CTR</t>
+  </si>
+  <si>
+    <t>11171-000001</t>
+  </si>
+  <si>
+    <t>100ml weight</t>
   </si>
 </sst>
 </file>
@@ -283,7 +268,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -368,6 +353,12 @@
     <font>
       <vertAlign val="subscript"/>
       <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -654,7 +645,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -738,12 +729,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -763,6 +748,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1155,13 +1143,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1278,7 +1266,7 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="11" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1"/>
       <c r="G5" s="1"/>
@@ -1315,7 +1303,7 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1338,8 +1326,9 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="11" t="s">
-        <v>75</v>
+      <c r="D7" s="11" t="str">
+        <f>D5</f>
+        <v>REF CTR</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -1370,8 +1359,9 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="11" t="s">
-        <v>76</v>
+      <c r="D8" s="11" t="str">
+        <f>D6</f>
+        <v>11171-000001</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -1403,7 +1393,7 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="15">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -1450,9 +1440,7 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="20">
-        <v>35</v>
-      </c>
+      <c r="D11" s="20"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1473,8 +1461,8 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="11">
-        <v>12704</v>
+      <c r="D12" s="59">
+        <v>10443</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -1681,7 +1669,7 @@
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="15">
-        <v>46188</v>
+        <v>46196</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1730,7 +1718,7 @@
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="11" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I23" s="1"/>
       <c r="K23" s="1" t="s">
@@ -1751,11 +1739,11 @@
         <v>49</v>
       </c>
       <c r="C24" s="30">
-        <v>5868.8</v>
+        <v>8793.1</v>
       </c>
       <c r="D24" s="31">
         <f>(C24-$C$30)/$C$30</f>
-        <v>1.588708365212526E-2</v>
+        <v>8.1818536209518501E-3</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1778,19 +1766,21 @@
         <v>50</v>
       </c>
       <c r="C25" s="32">
-        <v>5920.8</v>
+        <v>8667.1</v>
       </c>
       <c r="D25" s="31">
         <f>(C25-$C$30)/$C$30</f>
-        <v>2.4888264191572935E-2</v>
+        <v>-6.2648049586435071E-3</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="1"/>
+      <c r="F25" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="48"/>
+      <c r="H25" s="49">
+        <v>85.4</v>
+      </c>
+      <c r="I25" s="50"/>
       <c r="K25" s="1" t="s">
         <v>48</v>
       </c>
@@ -1802,48 +1792,52 @@
     <row r="26" spans="1:18" ht="13.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="32">
-        <v>5789.5</v>
+        <v>8677.9</v>
       </c>
       <c r="D26" s="31">
         <f>(C26-$C$30)/$C$30</f>
-        <v>2.1602833294675238E-3</v>
+        <v>-5.0265199375354166E-3</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="1" t="s">
-        <v>53</v>
+      <c r="F26" s="51" t="s">
+        <v>59</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="11">
         <v>20</v>
       </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="52" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="27" spans="1:18" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="32">
-        <v>5707.8</v>
+        <v>8736.7999999999993</v>
       </c>
       <c r="D27" s="31">
         <f>(C27-$C$30)/$C$30</f>
-        <v>-1.198195609501081E-2</v>
+        <v>1.7267196683230057E-3</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>55</v>
+      <c r="F27" s="51" t="s">
+        <v>61</v>
       </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="29">
-        <v>85.33</v>
-      </c>
-      <c r="I27" s="1"/>
+      <c r="H27" s="11">
+        <v>50</v>
+      </c>
+      <c r="I27" s="52" t="s">
+        <v>11</v>
+      </c>
       <c r="K27" s="33" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="35"/>
@@ -1851,27 +1845,29 @@
     <row r="28" spans="1:18" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C28" s="36">
-        <v>5598.2</v>
+        <v>8733.7999999999993</v>
       </c>
       <c r="D28" s="31">
         <f>(C28-$C$30)/$C$30</f>
-        <v>-3.0953675078154434E-2</v>
+        <v>1.3827516069040687E-3</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>58</v>
+      <c r="F28" s="51" t="s">
+        <v>62</v>
       </c>
       <c r="G28" s="1"/>
-      <c r="H28" s="29">
-        <f>H27/100</f>
-        <v>0.85329999999999995</v>
-      </c>
-      <c r="I28" s="1"/>
+      <c r="H28" s="11">
+        <f>H26+H27</f>
+        <v>70</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>11</v>
+      </c>
       <c r="K28" s="33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L28" s="34"/>
       <c r="M28" s="37">
@@ -1884,9 +1880,18 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="F29" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="29">
+        <v>25.88</v>
+      </c>
+      <c r="I29" s="52" t="s">
+        <v>64</v>
+      </c>
       <c r="K29" s="38" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L29" s="38"/>
       <c r="M29" s="39">
@@ -1897,46 +1902,46 @@
     <row r="30" spans="1:18" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C30" s="40">
         <f>AVERAGE(C24:C28)</f>
-        <v>5777.0199999999995</v>
+        <v>8721.74</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="50"/>
-      <c r="H30" s="51">
-        <v>85.33</v>
+      <c r="F30" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="29">
+        <f>H25-H29</f>
+        <v>59.52000000000001</v>
       </c>
       <c r="I30" s="52"/>
     </row>
     <row r="31" spans="1:18" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C31" s="40">
         <f>STDEVP(C24:C28)</f>
-        <v>114.90866633983715</v>
+        <v>45.545520087051386</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="11">
-        <v>20</v>
-      </c>
-      <c r="I31" s="54" t="s">
-        <v>11</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G31" s="42"/>
+      <c r="H31" s="43">
+        <f>H30/(H25/100)</f>
+        <v>69.695550351288063</v>
+      </c>
+      <c r="I31" s="52"/>
       <c r="K31" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M31" s="41">
         <f>(M29-1)*1000</f>
@@ -1949,16 +1954,10 @@
       <c r="C32" s="40"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="53" t="s">
-        <v>66</v>
-      </c>
+      <c r="F32" s="51"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="11">
-        <v>50</v>
-      </c>
-      <c r="I32" s="54" t="s">
-        <v>11</v>
-      </c>
+      <c r="H32" s="11"/>
+      <c r="I32" s="52"/>
     </row>
     <row r="33" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
@@ -1966,17 +1965,15 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="11">
-        <f>H31+H32</f>
-        <v>70</v>
-      </c>
-      <c r="I33" s="54" t="s">
-        <v>11</v>
-      </c>
+      <c r="F33" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56">
+        <f>H31/H28-1</f>
+        <v>-4.3492806958848051E-3</v>
+      </c>
+      <c r="I33" s="57"/>
     </row>
     <row r="34" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
@@ -1984,79 +1981,66 @@
       <c r="C34" s="31"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="29">
-        <v>26.18</v>
-      </c>
-      <c r="I34" s="54" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="35" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="F35" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="29">
-        <f>H30-H34</f>
-        <v>59.15</v>
-      </c>
-      <c r="I35" s="54"/>
     </row>
     <row r="36" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="F36" s="55" t="s">
+      <c r="F36" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="G36" s="42"/>
-      <c r="H36" s="43">
-        <f>H35/H28</f>
-        <v>69.319114027891715</v>
-      </c>
-      <c r="I36" s="54"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="49">
+        <v>85.11</v>
+      </c>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="F37" s="53"/>
+      <c r="F37" s="51" t="s">
+        <v>59</v>
+      </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="54"/>
+      <c r="H37" s="11">
+        <v>20</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="38" spans="1:10" ht="15.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C38" s="31">
         <f>C31/C30</f>
-        <v>1.9890647139846698E-2</v>
+        <v>5.2220680835534409E-3</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>IF(C38&lt;0.03,"&lt;3% = PASS","&gt;3% = FAIL")</f>
         <v>&lt;3% = PASS</v>
       </c>
-      <c r="F38" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="G38" s="57"/>
-      <c r="H38" s="58">
-        <f>H36/H33-1</f>
-        <v>-9.726942458689769E-3</v>
-      </c>
-      <c r="I38" s="59"/>
+      <c r="F38" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="11">
+        <v>50</v>
+      </c>
+      <c r="I38" s="52" t="s">
+        <v>11</v>
+      </c>
       <c r="J38" s="44"/>
     </row>
     <row r="39" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
@@ -2064,52 +2048,80 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="F39" s="1"/>
+      <c r="F39" s="51" t="s">
+        <v>62</v>
+      </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="44"/>
+      <c r="H39" s="11">
+        <f>H37+H38</f>
+        <v>70</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>11</v>
+      </c>
       <c r="J39" s="44"/>
     </row>
     <row r="40" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
-      <c r="F40" s="1"/>
+      <c r="F40" s="51" t="s">
+        <v>63</v>
+      </c>
       <c r="G40" s="1"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="44"/>
+      <c r="H40" s="29">
+        <v>26.33</v>
+      </c>
+      <c r="I40" s="52" t="s">
+        <v>64</v>
+      </c>
       <c r="J40" s="44"/>
     </row>
     <row r="41" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B41" s="47"/>
+      <c r="B41" s="45"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="F41" s="51" t="s">
+        <v>65</v>
+      </c>
       <c r="G41" s="1"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="44"/>
+      <c r="H41" s="29">
+        <f>H36-H40</f>
+        <v>58.78</v>
+      </c>
+      <c r="I41" s="52"/>
       <c r="J41" s="44"/>
     </row>
     <row r="42" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="44"/>
+      <c r="F42" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="42"/>
+      <c r="H42" s="43">
+        <f>H41/(H36/100)</f>
+        <v>69.063564798496074</v>
+      </c>
+      <c r="I42" s="52"/>
       <c r="J42" s="44"/>
     </row>
     <row r="43" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="F43" s="51"/>
       <c r="G43" s="1"/>
       <c r="H43" s="11"/>
-      <c r="I43" s="44"/>
+      <c r="I43" s="52"/>
       <c r="J43" s="44"/>
     </row>
     <row r="44" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="C44" s="6"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="44"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="55"/>
+      <c r="H44" s="56">
+        <f>H42/H39-1</f>
+        <v>-1.3377645735770383E-2</v>
+      </c>
+      <c r="I44" s="57"/>
       <c r="J44" s="44"/>
     </row>
     <row r="45" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
@@ -2128,10 +2140,14 @@
     </row>
     <row r="47" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="1"/>
+      <c r="F47" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G47" s="48"/>
+      <c r="H47" s="49">
+        <v>86.24</v>
+      </c>
+      <c r="I47" s="50"/>
     </row>
     <row r="48" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A48" s="1"/>
@@ -2139,10 +2155,16 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
+      <c r="F48" s="51" t="s">
+        <v>59</v>
+      </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="1"/>
+      <c r="H48" s="11">
+        <v>20</v>
+      </c>
+      <c r="I48" s="52" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="49" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A49" s="1"/>
@@ -2150,10 +2172,16 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="F49" s="51" t="s">
+        <v>61</v>
+      </c>
       <c r="G49" s="1"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="1"/>
+      <c r="H49" s="11">
+        <v>50</v>
+      </c>
+      <c r="I49" s="52" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="50" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A50" s="1"/>
@@ -2161,30 +2189,68 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="I50" s="31"/>
+      <c r="F50" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="11">
+        <f>H48+H49</f>
+        <v>70</v>
+      </c>
+      <c r="I50" s="52" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="51" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="F51" s="1"/>
+      <c r="F51" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="29">
+        <v>27.6</v>
+      </c>
+      <c r="I51" s="52" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="52" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="F52" s="1"/>
+      <c r="F52" s="51" t="s">
+        <v>65</v>
+      </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="11"/>
+      <c r="H52" s="29">
+        <f>H47-H51</f>
+        <v>58.639999999999993</v>
+      </c>
+      <c r="I52" s="52"/>
     </row>
     <row r="53" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="11"/>
+      <c r="F53" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="G53" s="42"/>
+      <c r="H53" s="43">
+        <f>H52/(H47/100)</f>
+        <v>67.996289424860848</v>
+      </c>
+      <c r="I53" s="52"/>
     </row>
     <row r="54" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="F54" s="1"/>
+      <c r="F54" s="51"/>
       <c r="G54" s="1"/>
       <c r="H54" s="11"/>
+      <c r="I54" s="52"/>
     </row>
     <row r="55" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="29"/>
+      <c r="F55" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G55" s="55"/>
+      <c r="H55" s="56">
+        <f>H53/H50-1</f>
+        <v>-2.8624436787702212E-2</v>
+      </c>
+      <c r="I55" s="57"/>
     </row>
     <row r="56" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F56" s="1"/>
